--- a/games/cozy-grove/cozy-grove_data.xlsx
+++ b/games/cozy-grove/cozy-grove_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubChelsea\Achievement-Vault\games\cozy-grove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3129845-060D-499E-BE46-C72A1848D75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB92AB29-FA9B-4D84-BDE6-1450CD4E20B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="1005" windowWidth="21600" windowHeight="13830" xr2:uid="{E79D6183-D772-F644-AE89-4CAD504C8F4D}"/>
+    <workbookView xWindow="1620" yWindow="1035" windowWidth="21600" windowHeight="13830" xr2:uid="{E79D6183-D772-F644-AE89-4CAD504C8F4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6124,16 +6124,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -6475,213 +6471,213 @@
   <dimension ref="A1:BP255"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="32.5" style="3" customWidth="1"/>
-    <col min="3" max="4" width="6.5" style="3" customWidth="1"/>
+    <col min="1" max="2" width="32.5" customWidth="1"/>
+    <col min="3" max="4" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:68" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="O1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T1" s="2" t="s">
+      <c r="S1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="3" t="s">
         <v>1279</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X1" s="2" t="s">
+      <c r="W1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="3" t="s">
         <v>1281</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="3" t="s">
         <v>1282</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AK1" s="3" t="s">
         <v>1283</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AO1" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AQ1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AS1" s="5" t="s">
+      <c r="AS1" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AU1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AU1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AW1" s="3" t="s">
         <v>1286</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AY1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AY1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BA1" s="5" t="s">
+      <c r="BA1" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BC1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BC1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BE1" s="5" t="s">
+      <c r="BE1" s="3" t="s">
         <v>1287</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BG1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BG1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BI1" s="5" t="s">
+      <c r="BI1" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BK1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BK1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BM1" s="5" t="s">
+      <c r="BM1" s="3" t="s">
         <v>1290</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BN1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BO1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BO1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6692,7 +6688,7 @@
       <c r="B2" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
@@ -6847,7 +6843,7 @@
       <c r="B3" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="E3" t="s">
@@ -7002,7 +6998,7 @@
       <c r="B4" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
@@ -7157,7 +7153,7 @@
       <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -7315,7 +7311,10 @@
       <c r="B6" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
@@ -7388,6 +7387,9 @@
         <v>1490</v>
       </c>
       <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
@@ -7473,7 +7475,7 @@
       <c r="B7" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="E7" t="s">
@@ -7634,7 +7636,7 @@
       <c r="B8" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="E8" t="s">
@@ -7795,7 +7797,7 @@
       <c r="B9" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="E9" t="s">
@@ -7956,7 +7958,7 @@
       <c r="B10" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>1</v>
       </c>
       <c r="E10" t="s">
@@ -8120,7 +8122,7 @@
       <c r="B11" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>1</v>
       </c>
       <c r="E11" t="s">
@@ -8169,6 +8171,9 @@
         <v>1316</v>
       </c>
       <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11" t="s">
@@ -8287,7 +8292,7 @@
       <c r="B12" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
       <c r="E12" t="s">
@@ -8454,7 +8459,7 @@
       <c r="B13" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>1</v>
       </c>
       <c r="E13" t="s">
@@ -8621,7 +8626,7 @@
       <c r="B14" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="E14" t="s">
@@ -8788,10 +8793,10 @@
       <c r="B15" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4"/>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2"/>
       <c r="E15" t="s">
         <v>272</v>
       </c>
@@ -8838,6 +8843,9 @@
         <v>1320</v>
       </c>
       <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15" t="s">
@@ -8956,10 +8964,10 @@
       <c r="B16" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4"/>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2"/>
       <c r="E16" t="s">
         <v>273</v>
       </c>
@@ -9127,10 +9135,10 @@
       <c r="B17" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="E17" t="s">
         <v>274</v>
       </c>
@@ -9301,10 +9309,10 @@
       <c r="B18" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4"/>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2"/>
       <c r="E18" t="s">
         <v>275</v>
       </c>
@@ -9478,10 +9486,10 @@
       <c r="B19" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4"/>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2"/>
       <c r="E19" t="s">
         <v>276</v>
       </c>
@@ -9661,10 +9669,10 @@
       <c r="B20" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4"/>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2"/>
       <c r="E20" t="s">
         <v>277</v>
       </c>
@@ -9840,6 +9848,9 @@
         <v>1988</v>
       </c>
       <c r="BO20">
+        <v>1</v>
+      </c>
+      <c r="BP20">
         <v>1</v>
       </c>
     </row>
@@ -9850,10 +9861,10 @@
       <c r="B21" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="4">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4"/>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2"/>
       <c r="E21" t="s">
         <v>278</v>
       </c>
@@ -10045,10 +10056,10 @@
       <c r="B22" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="4">
-        <v>1</v>
-      </c>
-      <c r="D22" s="4"/>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2"/>
       <c r="E22" t="s">
         <v>279</v>
       </c>
@@ -10240,10 +10251,10 @@
       <c r="B23" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="4">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4"/>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2"/>
       <c r="E23" t="s">
         <v>280</v>
       </c>
@@ -10435,10 +10446,10 @@
       <c r="B24" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="4">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4"/>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2"/>
       <c r="E24" t="s">
         <v>281</v>
       </c>
@@ -10630,10 +10641,10 @@
       <c r="B25" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="4">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4"/>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2"/>
       <c r="E25" t="s">
         <v>282</v>
       </c>
@@ -10828,10 +10839,10 @@
       <c r="B26" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4"/>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2"/>
       <c r="E26" t="s">
         <v>283</v>
       </c>
@@ -11026,7 +11037,7 @@
       <c r="B27" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>1</v>
       </c>
       <c r="E27" t="s">
@@ -11223,7 +11234,7 @@
       <c r="B28" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>1</v>
       </c>
       <c r="E28" t="s">
@@ -11420,7 +11431,7 @@
       <c r="B29" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="E29" t="s">
@@ -11617,7 +11628,7 @@
       <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>1</v>
       </c>
       <c r="E30" t="s">
@@ -11814,7 +11825,7 @@
       <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="E31" t="s">
@@ -12011,7 +12022,7 @@
       <c r="B32" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <v>1</v>
       </c>
       <c r="E32" t="s">
@@ -12064,7 +12075,7 @@
       <c r="B33" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="E33" t="s">
@@ -12117,7 +12128,7 @@
       <c r="B34" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2">
         <v>1</v>
       </c>
       <c r="E34" t="s">
@@ -12170,7 +12181,7 @@
       <c r="B35" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <v>1</v>
       </c>
       <c r="E35" t="s">
@@ -12223,7 +12234,7 @@
       <c r="B36" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="2">
         <v>1</v>
       </c>
       <c r="E36" t="s">
@@ -12276,7 +12287,7 @@
       <c r="B37" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="2">
         <v>1</v>
       </c>
       <c r="E37" t="s">
@@ -12329,7 +12340,7 @@
       <c r="B38" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="2">
         <v>1</v>
       </c>
       <c r="E38" t="s">
@@ -12382,7 +12393,7 @@
       <c r="B39" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="E39" t="s">
@@ -12435,7 +12446,7 @@
       <c r="B40" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2">
         <v>1</v>
       </c>
       <c r="E40" t="s">
@@ -12488,7 +12499,7 @@
       <c r="B41" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="2">
         <v>1</v>
       </c>
       <c r="E41" t="s">
@@ -12541,7 +12552,7 @@
       <c r="B42" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="2">
         <v>1</v>
       </c>
       <c r="E42" t="s">
@@ -12594,7 +12605,7 @@
       <c r="B43" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="E43" t="s">
@@ -12647,7 +12658,7 @@
       <c r="B44" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="2">
         <v>1</v>
       </c>
       <c r="E44" t="s">
@@ -12700,7 +12711,7 @@
       <c r="B45" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="2">
         <v>1</v>
       </c>
       <c r="E45" t="s">
@@ -12753,7 +12764,7 @@
       <c r="B46" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="2">
         <v>1</v>
       </c>
       <c r="E46" t="s">
@@ -12806,7 +12817,7 @@
       <c r="B47" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="2">
         <v>1</v>
       </c>
       <c r="E47" t="s">
@@ -12859,7 +12870,7 @@
       <c r="B48" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="2">
         <v>1</v>
       </c>
       <c r="E48" t="s">
@@ -12912,7 +12923,7 @@
       <c r="B49" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="2">
         <v>1</v>
       </c>
       <c r="E49" t="s">
@@ -12965,7 +12976,7 @@
       <c r="B50" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="2">
         <v>1</v>
       </c>
       <c r="E50" t="s">
@@ -13018,7 +13029,7 @@
       <c r="B51" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="2">
         <v>1</v>
       </c>
       <c r="E51" t="s">
@@ -13071,7 +13082,7 @@
       <c r="B52" t="s">
         <v>112</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="2">
         <v>1</v>
       </c>
       <c r="E52" t="s">
@@ -13124,7 +13135,7 @@
       <c r="B53" t="s">
         <v>89</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="E53" t="s">
@@ -13177,7 +13188,7 @@
       <c r="B54" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="2">
         <v>1</v>
       </c>
       <c r="E54" t="s">
@@ -13230,7 +13241,7 @@
       <c r="B55" t="s">
         <v>113</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="2">
         <v>1</v>
       </c>
       <c r="E55" t="s">
@@ -13283,7 +13294,7 @@
       <c r="B56" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="E56" t="s">
@@ -13336,7 +13347,7 @@
       <c r="B57" t="s">
         <v>98</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="E57" t="s">
@@ -13389,7 +13400,7 @@
       <c r="B58" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="E58" t="s">
@@ -13442,7 +13453,7 @@
       <c r="B59" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="E59" t="s">
@@ -13495,7 +13506,7 @@
       <c r="B60" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="2">
         <v>1</v>
       </c>
       <c r="E60" t="s">
@@ -13548,7 +13559,7 @@
       <c r="B61" t="s">
         <v>98</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="2">
         <v>1</v>
       </c>
       <c r="E61" t="s">
@@ -13601,7 +13612,7 @@
       <c r="B62" t="s">
         <v>115</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="2">
         <v>1</v>
       </c>
       <c r="E62" t="s">
@@ -13654,7 +13665,7 @@
       <c r="B63" t="s">
         <v>115</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="2">
         <v>1</v>
       </c>
       <c r="E63" t="s">
@@ -13707,7 +13718,7 @@
       <c r="B64" t="s">
         <v>116</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="2">
         <v>1</v>
       </c>
       <c r="E64" t="s">
@@ -13753,14 +13764,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="B65" t="s">
         <v>116</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="2">
         <v>1</v>
       </c>
       <c r="E65" t="s">
@@ -13806,14 +13817,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="B66" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="2">
         <v>1</v>
       </c>
       <c r="E66" t="s">
@@ -13859,14 +13870,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
       <c r="B67" t="s">
         <v>117</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="2">
         <v>1</v>
       </c>
       <c r="E67" t="s">
@@ -13912,14 +13923,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
       <c r="B68" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="2">
         <v>1</v>
       </c>
       <c r="E68" t="s">
@@ -13965,14 +13976,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
       <c r="B69" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="2">
         <v>1</v>
       </c>
       <c r="E69" t="s">
@@ -14017,15 +14028,18 @@
       <c r="S69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
       <c r="B70" t="s">
         <v>102</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="2">
         <v>1</v>
       </c>
       <c r="E70" t="s">
@@ -14059,14 +14073,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
       <c r="B71" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="2">
         <v>1</v>
       </c>
       <c r="E71" t="s">
@@ -14100,14 +14114,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
       <c r="B72" t="s">
         <v>118</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="2">
         <v>1</v>
       </c>
       <c r="E72" t="s">
@@ -14141,14 +14155,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
       <c r="B73" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="2">
         <v>1</v>
       </c>
       <c r="E73" t="s">
@@ -14182,14 +14196,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
       <c r="B74" t="s">
         <v>117</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="2">
         <v>1</v>
       </c>
       <c r="E74" t="s">
@@ -14223,14 +14237,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
       <c r="B75" t="s">
         <v>116</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="2">
         <v>1</v>
       </c>
       <c r="E75" t="s">
@@ -14264,14 +14278,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
       <c r="B76" t="s">
         <v>91</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="2">
         <v>1</v>
       </c>
       <c r="E76" t="s">
@@ -14305,14 +14319,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
       <c r="B77" t="s">
         <v>106</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="2">
         <v>1</v>
       </c>
       <c r="E77" t="s">
@@ -14346,14 +14360,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
       <c r="B78" t="s">
         <v>97</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="E78" t="s">
@@ -14387,14 +14401,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
       <c r="B79" t="s">
         <v>112</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="2">
         <v>1</v>
       </c>
       <c r="E79" t="s">
@@ -14428,14 +14442,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
       <c r="B80" t="s">
         <v>112</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" t="s">
@@ -14476,7 +14493,7 @@
       <c r="B81" t="s">
         <v>117</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="2">
         <v>1</v>
       </c>
       <c r="E81" t="s">
@@ -14517,7 +14534,7 @@
       <c r="B82" t="s">
         <v>89</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="2">
         <v>1</v>
       </c>
       <c r="E82" t="s">
@@ -14558,7 +14575,7 @@
       <c r="B83" t="s">
         <v>98</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="2">
         <v>1</v>
       </c>
       <c r="E83" t="s">
@@ -14599,7 +14616,7 @@
       <c r="B84" t="s">
         <v>109</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="2">
         <v>1</v>
       </c>
       <c r="E84" t="s">
@@ -14640,7 +14657,7 @@
       <c r="B85" t="s">
         <v>115</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="2">
         <v>1</v>
       </c>
       <c r="E85" t="s">
@@ -14681,10 +14698,10 @@
       <c r="B86" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="4">
-        <v>1</v>
-      </c>
-      <c r="D86" s="4">
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
         <v>1</v>
       </c>
       <c r="E86" t="s">
@@ -14725,10 +14742,10 @@
       <c r="B87" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="4">
-        <v>1</v>
-      </c>
-      <c r="D87" s="4">
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
         <v>1</v>
       </c>
       <c r="E87" t="s">
@@ -14769,10 +14786,10 @@
       <c r="B88" t="s">
         <v>121</v>
       </c>
-      <c r="C88" s="4">
-        <v>1</v>
-      </c>
-      <c r="D88" s="4">
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
         <v>1</v>
       </c>
       <c r="E88" t="s">
@@ -14813,10 +14830,10 @@
       <c r="B89" t="s">
         <v>105</v>
       </c>
-      <c r="C89" s="4">
-        <v>1</v>
-      </c>
-      <c r="D89" s="4">
+      <c r="C89" s="2">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
         <v>1</v>
       </c>
       <c r="E89" t="s">
@@ -14860,10 +14877,10 @@
       <c r="B90" t="s">
         <v>122</v>
       </c>
-      <c r="C90" s="4">
-        <v>1</v>
-      </c>
-      <c r="D90" s="4">
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2">
         <v>1</v>
       </c>
       <c r="E90" t="s">
@@ -14907,10 +14924,10 @@
       <c r="B91" t="s">
         <v>123</v>
       </c>
-      <c r="C91" s="4">
-        <v>1</v>
-      </c>
-      <c r="D91" s="4">
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
         <v>1</v>
       </c>
       <c r="E91" t="s">
@@ -14954,10 +14971,10 @@
       <c r="B92" t="s">
         <v>124</v>
       </c>
-      <c r="C92" s="4">
-        <v>1</v>
-      </c>
-      <c r="D92" s="4">
+      <c r="C92" s="2">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2">
         <v>1</v>
       </c>
       <c r="E92" t="s">
@@ -15001,10 +15018,10 @@
       <c r="B93" t="s">
         <v>125</v>
       </c>
-      <c r="C93" s="4">
-        <v>1</v>
-      </c>
-      <c r="D93" s="4">
+      <c r="C93" s="2">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
         <v>1</v>
       </c>
       <c r="E93" t="s">
@@ -15048,10 +15065,10 @@
       <c r="B94" t="s">
         <v>126</v>
       </c>
-      <c r="C94" s="4">
-        <v>1</v>
-      </c>
-      <c r="D94" s="4">
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
         <v>1</v>
       </c>
       <c r="E94" t="s">
@@ -15095,10 +15112,10 @@
       <c r="B95" t="s">
         <v>122</v>
       </c>
-      <c r="C95" s="4">
-        <v>1</v>
-      </c>
-      <c r="D95" s="4">
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
         <v>1</v>
       </c>
       <c r="E95" t="s">
@@ -15142,10 +15159,10 @@
       <c r="B96" t="s">
         <v>120</v>
       </c>
-      <c r="C96" s="4">
-        <v>1</v>
-      </c>
-      <c r="D96" s="4">
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2">
         <v>1</v>
       </c>
       <c r="E96" t="s">
@@ -15182,17 +15199,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>160</v>
       </c>
       <c r="B97" t="s">
         <v>127</v>
       </c>
-      <c r="C97" s="4">
-        <v>1</v>
-      </c>
-      <c r="D97" s="4">
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
         <v>1</v>
       </c>
       <c r="E97" t="s">
@@ -15228,18 +15245,21 @@
       <c r="S97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>161</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
       </c>
-      <c r="C98" s="4">
-        <v>1</v>
-      </c>
-      <c r="D98" s="4">
+      <c r="C98" s="2">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2">
         <v>1</v>
       </c>
       <c r="E98" t="s">
@@ -15276,17 +15296,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>162</v>
       </c>
       <c r="B99" t="s">
         <v>129</v>
       </c>
-      <c r="C99" s="4">
-        <v>1</v>
-      </c>
-      <c r="D99" s="4">
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2">
         <v>1</v>
       </c>
       <c r="E99" t="s">
@@ -15323,17 +15343,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>163</v>
       </c>
       <c r="B100" t="s">
         <v>130</v>
       </c>
-      <c r="C100" s="4">
-        <v>1</v>
-      </c>
-      <c r="D100" s="4">
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2">
         <v>1</v>
       </c>
       <c r="E100" t="s">
@@ -15370,17 +15390,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>164</v>
       </c>
       <c r="B101" t="s">
         <v>120</v>
       </c>
-      <c r="C101" s="4">
-        <v>1</v>
-      </c>
-      <c r="D101" s="4">
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2">
         <v>1</v>
       </c>
       <c r="E101" t="s">
@@ -15417,17 +15437,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>165</v>
       </c>
       <c r="B102" t="s">
         <v>131</v>
       </c>
-      <c r="C102" s="4">
-        <v>1</v>
-      </c>
-      <c r="D102" s="4">
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2">
         <v>1</v>
       </c>
       <c r="E102" t="s">
@@ -15464,17 +15484,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>166</v>
       </c>
       <c r="B103" t="s">
         <v>132</v>
       </c>
-      <c r="C103" s="4">
-        <v>1</v>
-      </c>
-      <c r="D103" s="4">
+      <c r="C103" s="2">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2">
         <v>1</v>
       </c>
       <c r="E103" t="s">
@@ -15511,17 +15531,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>167</v>
       </c>
       <c r="B104" t="s">
         <v>133</v>
       </c>
-      <c r="C104" s="4">
-        <v>1</v>
-      </c>
-      <c r="D104" s="4">
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2">
         <v>1</v>
       </c>
       <c r="E104" t="s">
@@ -15558,17 +15578,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
       <c r="B105" t="s">
         <v>124</v>
       </c>
-      <c r="C105" s="4">
-        <v>1</v>
-      </c>
-      <c r="D105" s="4">
+      <c r="C105" s="2">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2">
         <v>1</v>
       </c>
       <c r="E105" t="s">
@@ -15605,17 +15625,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>169</v>
       </c>
       <c r="B106" t="s">
         <v>134</v>
       </c>
-      <c r="C106" s="4">
-        <v>1</v>
-      </c>
-      <c r="D106" s="4">
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2">
         <v>1</v>
       </c>
       <c r="E106" t="s">
@@ -15652,17 +15672,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>170</v>
       </c>
       <c r="B107" t="s">
         <v>135</v>
       </c>
-      <c r="C107" s="4">
-        <v>1</v>
-      </c>
-      <c r="D107" s="4">
+      <c r="C107" s="2">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2">
         <v>1</v>
       </c>
       <c r="E107" t="s">
@@ -15699,17 +15719,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>171</v>
       </c>
       <c r="B108" t="s">
         <v>136</v>
       </c>
-      <c r="C108" s="4">
-        <v>1</v>
-      </c>
-      <c r="D108" s="4">
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D108" s="2">
         <v>1</v>
       </c>
       <c r="E108" t="s">
@@ -15746,17 +15766,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>172</v>
       </c>
       <c r="B109" t="s">
         <v>137</v>
       </c>
-      <c r="C109" s="4">
-        <v>1</v>
-      </c>
-      <c r="D109" s="4">
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2">
         <v>1</v>
       </c>
       <c r="E109" t="s">
@@ -15793,17 +15813,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>173</v>
       </c>
       <c r="B110" t="s">
         <v>138</v>
       </c>
-      <c r="C110" s="4">
-        <v>1</v>
-      </c>
-      <c r="D110" s="4">
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2">
         <v>1</v>
       </c>
       <c r="E110" t="s">
@@ -15840,17 +15860,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>174</v>
       </c>
       <c r="B111" t="s">
         <v>128</v>
       </c>
-      <c r="C111" s="4">
-        <v>1</v>
-      </c>
-      <c r="D111" s="4">
+      <c r="C111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2">
         <v>1</v>
       </c>
       <c r="E111" t="s">
@@ -15887,17 +15907,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>175</v>
       </c>
       <c r="B112" t="s">
         <v>139</v>
       </c>
-      <c r="C112" s="4">
-        <v>1</v>
-      </c>
-      <c r="D112" s="4">
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2">
         <v>1</v>
       </c>
       <c r="E112" t="s">
@@ -15941,10 +15961,10 @@
       <c r="B113" t="s">
         <v>140</v>
       </c>
-      <c r="C113" s="4">
-        <v>1</v>
-      </c>
-      <c r="D113" s="4">
+      <c r="C113" s="2">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2">
         <v>1</v>
       </c>
       <c r="E113" t="s">
@@ -15988,10 +16008,10 @@
       <c r="B114" t="s">
         <v>96</v>
       </c>
-      <c r="C114" s="4">
-        <v>1</v>
-      </c>
-      <c r="D114" s="4">
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
         <v>1</v>
       </c>
       <c r="E114" t="s">
@@ -16035,10 +16055,10 @@
       <c r="B115" t="s">
         <v>141</v>
       </c>
-      <c r="C115" s="4">
-        <v>1</v>
-      </c>
-      <c r="D115" s="4">
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2">
         <v>1</v>
       </c>
       <c r="E115" t="s">
@@ -16082,10 +16102,10 @@
       <c r="B116" t="s">
         <v>119</v>
       </c>
-      <c r="C116" s="4">
-        <v>1</v>
-      </c>
-      <c r="D116" s="4">
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2">
         <v>1</v>
       </c>
       <c r="E116" t="s">
@@ -16129,10 +16149,10 @@
       <c r="B117" t="s">
         <v>142</v>
       </c>
-      <c r="C117" s="4">
-        <v>1</v>
-      </c>
-      <c r="D117" s="4">
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
         <v>1</v>
       </c>
       <c r="E117" t="s">
@@ -16176,10 +16196,10 @@
       <c r="B118" t="s">
         <v>113</v>
       </c>
-      <c r="C118" s="4">
-        <v>1</v>
-      </c>
-      <c r="D118" s="4">
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2">
         <v>1</v>
       </c>
       <c r="E118" t="s">
@@ -16223,10 +16243,10 @@
       <c r="B119" t="s">
         <v>143</v>
       </c>
-      <c r="C119" s="4">
-        <v>1</v>
-      </c>
-      <c r="D119" s="4">
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
         <v>1</v>
       </c>
       <c r="E119" t="s">
@@ -16270,10 +16290,10 @@
       <c r="B120" t="s">
         <v>144</v>
       </c>
-      <c r="C120" s="4">
-        <v>1</v>
-      </c>
-      <c r="D120" s="4">
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
         <v>1</v>
       </c>
       <c r="E120" t="s">
@@ -16317,10 +16337,10 @@
       <c r="B121" t="s">
         <v>127</v>
       </c>
-      <c r="C121" s="4">
-        <v>1</v>
-      </c>
-      <c r="D121" s="4">
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
         <v>1</v>
       </c>
       <c r="E121" t="s">
@@ -16364,10 +16384,10 @@
       <c r="B122" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="4">
-        <v>1</v>
-      </c>
-      <c r="D122" s="4">
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2">
         <v>1</v>
       </c>
       <c r="E122" t="s">
@@ -16411,10 +16431,10 @@
       <c r="B123" t="s">
         <v>146</v>
       </c>
-      <c r="C123" s="4">
-        <v>1</v>
-      </c>
-      <c r="D123" s="4">
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
         <v>1</v>
       </c>
       <c r="E123" t="s">
@@ -16458,10 +16478,10 @@
       <c r="B124" t="s">
         <v>143</v>
       </c>
-      <c r="C124" s="4">
-        <v>1</v>
-      </c>
-      <c r="D124" s="4">
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+      <c r="D124" s="2">
         <v>1</v>
       </c>
       <c r="E124" t="s">
@@ -16505,10 +16525,10 @@
       <c r="B125" t="s">
         <v>119</v>
       </c>
-      <c r="C125" s="4">
-        <v>1</v>
-      </c>
-      <c r="D125" s="4">
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
         <v>1</v>
       </c>
       <c r="E125" t="s">
@@ -16552,10 +16572,10 @@
       <c r="B126" t="s">
         <v>143</v>
       </c>
-      <c r="C126" s="4">
-        <v>1</v>
-      </c>
-      <c r="D126" s="4">
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
         <v>1</v>
       </c>
       <c r="E126" t="s">
@@ -16587,10 +16607,10 @@
       <c r="B127" t="s">
         <v>135</v>
       </c>
-      <c r="C127" s="4">
-        <v>1</v>
-      </c>
-      <c r="D127" s="4">
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2">
         <v>1</v>
       </c>
       <c r="E127" t="s">
@@ -16622,10 +16642,10 @@
       <c r="B128" t="s">
         <v>125</v>
       </c>
-      <c r="C128" s="4">
-        <v>1</v>
-      </c>
-      <c r="D128" s="4">
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2">
         <v>1</v>
       </c>
       <c r="E128" t="s">
@@ -16657,10 +16677,10 @@
       <c r="B129" t="s">
         <v>138</v>
       </c>
-      <c r="C129" s="4">
-        <v>1</v>
-      </c>
-      <c r="D129" s="4">
+      <c r="C129" s="2">
+        <v>1</v>
+      </c>
+      <c r="D129" s="2">
         <v>1</v>
       </c>
       <c r="E129" t="s">
@@ -16692,10 +16712,10 @@
       <c r="B130" t="s">
         <v>114</v>
       </c>
-      <c r="C130" s="4">
-        <v>1</v>
-      </c>
-      <c r="D130" s="4">
+      <c r="C130" s="2">
+        <v>1</v>
+      </c>
+      <c r="D130" s="2">
         <v>1</v>
       </c>
       <c r="E130" t="s">
@@ -16727,10 +16747,10 @@
       <c r="B131" t="s">
         <v>140</v>
       </c>
-      <c r="C131" s="4">
-        <v>1</v>
-      </c>
-      <c r="D131" s="4">
+      <c r="C131" s="2">
+        <v>1</v>
+      </c>
+      <c r="D131" s="2">
         <v>1</v>
       </c>
       <c r="E131" t="s">
@@ -16762,10 +16782,10 @@
       <c r="B132" t="s">
         <v>111</v>
       </c>
-      <c r="C132" s="4">
-        <v>1</v>
-      </c>
-      <c r="D132" s="4">
+      <c r="C132" s="2">
+        <v>1</v>
+      </c>
+      <c r="D132" s="2">
         <v>1</v>
       </c>
       <c r="E132" t="s">
@@ -16797,10 +16817,10 @@
       <c r="B133" t="s">
         <v>147</v>
       </c>
-      <c r="C133" s="4">
-        <v>1</v>
-      </c>
-      <c r="D133" s="4">
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2">
         <v>1</v>
       </c>
       <c r="E133" t="s">
@@ -16832,10 +16852,10 @@
       <c r="B134" t="s">
         <v>122</v>
       </c>
-      <c r="C134" s="4">
-        <v>1</v>
-      </c>
-      <c r="D134" s="4">
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
         <v>1</v>
       </c>
       <c r="E134" t="s">
@@ -16867,10 +16887,10 @@
       <c r="B135" t="s">
         <v>126</v>
       </c>
-      <c r="C135" s="4">
-        <v>1</v>
-      </c>
-      <c r="D135" s="4">
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
         <v>1</v>
       </c>
       <c r="E135" t="s">
@@ -16902,10 +16922,10 @@
       <c r="B136" t="s">
         <v>127</v>
       </c>
-      <c r="C136" s="4">
-        <v>1</v>
-      </c>
-      <c r="D136" s="4">
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="2">
         <v>1</v>
       </c>
       <c r="E136" t="s">
@@ -16937,10 +16957,10 @@
       <c r="B137" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="4">
-        <v>1</v>
-      </c>
-      <c r="D137" s="4">
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2">
         <v>1</v>
       </c>
       <c r="E137" t="s">
@@ -16972,10 +16992,10 @@
       <c r="B138" t="s">
         <v>140</v>
       </c>
-      <c r="C138" s="4">
-        <v>1</v>
-      </c>
-      <c r="D138" s="4">
+      <c r="C138" s="2">
+        <v>1</v>
+      </c>
+      <c r="D138" s="2">
         <v>1</v>
       </c>
       <c r="E138" t="s">
@@ -17007,10 +17027,10 @@
       <c r="B139" t="s">
         <v>135</v>
       </c>
-      <c r="C139" s="4">
-        <v>1</v>
-      </c>
-      <c r="D139" s="4">
+      <c r="C139" s="2">
+        <v>1</v>
+      </c>
+      <c r="D139" s="2">
         <v>1</v>
       </c>
       <c r="E139" t="s">
@@ -17042,10 +17062,10 @@
       <c r="B140" t="s">
         <v>141</v>
       </c>
-      <c r="C140" s="4">
-        <v>1</v>
-      </c>
-      <c r="D140" s="4">
+      <c r="C140" s="2">
+        <v>1</v>
+      </c>
+      <c r="D140" s="2">
         <v>1</v>
       </c>
       <c r="E140" t="s">
@@ -17077,10 +17097,10 @@
       <c r="B141" t="s">
         <v>123</v>
       </c>
-      <c r="C141" s="4">
-        <v>1</v>
-      </c>
-      <c r="D141" s="4">
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
         <v>1</v>
       </c>
       <c r="E141" t="s">
@@ -17112,10 +17132,10 @@
       <c r="B142" t="s">
         <v>137</v>
       </c>
-      <c r="C142" s="4">
-        <v>1</v>
-      </c>
-      <c r="D142" s="4">
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
         <v>1</v>
       </c>
       <c r="E142" t="s">
@@ -17147,10 +17167,10 @@
       <c r="B143" t="s">
         <v>144</v>
       </c>
-      <c r="C143" s="4">
-        <v>1</v>
-      </c>
-      <c r="D143" s="4">
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
         <v>1</v>
       </c>
       <c r="E143" t="s">
@@ -17182,10 +17202,10 @@
       <c r="B144" t="s">
         <v>146</v>
       </c>
-      <c r="C144" s="4">
-        <v>1</v>
-      </c>
-      <c r="D144" s="4">
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
         <v>1</v>
       </c>
       <c r="E144" t="s">
@@ -17210,17 +17230,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>208</v>
       </c>
       <c r="B145" t="s">
         <v>130</v>
       </c>
-      <c r="C145" s="4">
-        <v>1</v>
-      </c>
-      <c r="D145" s="4">
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
         <v>1</v>
       </c>
       <c r="E145" t="s">
@@ -17245,17 +17265,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>209</v>
       </c>
       <c r="B146" t="s">
         <v>118</v>
       </c>
-      <c r="C146" s="4">
-        <v>1</v>
-      </c>
-      <c r="D146" s="4">
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
         <v>1</v>
       </c>
       <c r="E146" t="s">
@@ -17280,17 +17300,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
       <c r="B147" t="s">
         <v>136</v>
       </c>
-      <c r="C147" s="4">
-        <v>1</v>
-      </c>
-      <c r="D147" s="4">
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
         <v>1</v>
       </c>
       <c r="E147" t="s">
@@ -17315,17 +17335,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>211</v>
       </c>
       <c r="B148" t="s">
         <v>144</v>
       </c>
-      <c r="C148" s="4">
-        <v>1</v>
-      </c>
-      <c r="D148" s="4">
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2">
         <v>1</v>
       </c>
       <c r="E148" t="s">
@@ -17350,17 +17370,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>212</v>
       </c>
       <c r="B149" t="s">
         <v>128</v>
       </c>
-      <c r="C149" s="4">
-        <v>1</v>
-      </c>
-      <c r="D149" s="4">
+      <c r="C149" s="2">
+        <v>1</v>
+      </c>
+      <c r="D149" s="2">
         <v>1</v>
       </c>
       <c r="E149" t="s">
@@ -17384,18 +17404,21 @@
       <c r="S149">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>213</v>
       </c>
       <c r="B150" t="s">
         <v>100</v>
       </c>
-      <c r="C150" s="4">
-        <v>1</v>
-      </c>
-      <c r="D150" s="4">
+      <c r="C150" s="2">
+        <v>1</v>
+      </c>
+      <c r="D150" s="2">
         <v>1</v>
       </c>
       <c r="E150" t="s">
@@ -17420,17 +17443,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>214</v>
       </c>
       <c r="B151" t="s">
         <v>148</v>
       </c>
-      <c r="C151" s="4">
-        <v>1</v>
-      </c>
-      <c r="D151" s="4">
+      <c r="C151" s="2">
+        <v>1</v>
+      </c>
+      <c r="D151" s="2">
         <v>1</v>
       </c>
       <c r="E151" t="s">
@@ -17455,17 +17478,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>215</v>
       </c>
       <c r="B152" t="s">
         <v>132</v>
       </c>
-      <c r="C152" s="4">
-        <v>1</v>
-      </c>
-      <c r="D152" s="4">
+      <c r="C152" s="2">
+        <v>1</v>
+      </c>
+      <c r="D152" s="2">
         <v>1</v>
       </c>
       <c r="E152" t="s">
@@ -17490,17 +17513,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>216</v>
       </c>
       <c r="B153" t="s">
         <v>141</v>
       </c>
-      <c r="C153" s="4">
-        <v>1</v>
-      </c>
-      <c r="D153" s="4">
+      <c r="C153" s="2">
+        <v>1</v>
+      </c>
+      <c r="D153" s="2">
         <v>1</v>
       </c>
       <c r="E153" t="s">
@@ -17525,17 +17548,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>217</v>
       </c>
       <c r="B154" t="s">
         <v>134</v>
       </c>
-      <c r="C154" s="4">
-        <v>1</v>
-      </c>
-      <c r="D154" s="4">
+      <c r="C154" s="2">
+        <v>1</v>
+      </c>
+      <c r="D154" s="2">
         <v>1</v>
       </c>
       <c r="E154" t="s">
@@ -17560,17 +17583,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>218</v>
       </c>
       <c r="B155" t="s">
         <v>114</v>
       </c>
-      <c r="C155" s="4">
-        <v>1</v>
-      </c>
-      <c r="D155" s="4">
+      <c r="C155" s="2">
+        <v>1</v>
+      </c>
+      <c r="D155" s="2">
         <v>1</v>
       </c>
       <c r="E155" t="s">
@@ -17594,18 +17617,21 @@
       <c r="S155">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>219</v>
       </c>
       <c r="B156" t="s">
         <v>129</v>
       </c>
-      <c r="C156" s="4">
-        <v>1</v>
-      </c>
-      <c r="D156" s="4">
+      <c r="C156" s="2">
+        <v>1</v>
+      </c>
+      <c r="D156" s="2">
         <v>1</v>
       </c>
       <c r="E156" t="s">
@@ -17630,17 +17656,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>220</v>
       </c>
       <c r="B157" t="s">
         <v>137</v>
       </c>
-      <c r="C157" s="4">
-        <v>1</v>
-      </c>
-      <c r="D157" s="4">
+      <c r="C157" s="2">
+        <v>1</v>
+      </c>
+      <c r="D157" s="2">
         <v>1</v>
       </c>
       <c r="E157" t="s">
@@ -17665,17 +17691,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>221</v>
       </c>
       <c r="B158" t="s">
         <v>120</v>
       </c>
-      <c r="C158" s="4">
-        <v>1</v>
-      </c>
-      <c r="D158" s="4">
+      <c r="C158" s="2">
+        <v>1</v>
+      </c>
+      <c r="D158" s="2">
         <v>1</v>
       </c>
       <c r="E158" t="s">
@@ -17700,17 +17726,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>222</v>
       </c>
       <c r="B159" t="s">
         <v>125</v>
       </c>
-      <c r="C159" s="4">
-        <v>1</v>
-      </c>
-      <c r="D159" s="4">
+      <c r="C159" s="2">
+        <v>1</v>
+      </c>
+      <c r="D159" s="2">
         <v>1</v>
       </c>
       <c r="E159" t="s">
@@ -17735,17 +17761,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>223</v>
       </c>
       <c r="B160" t="s">
         <v>130</v>
       </c>
-      <c r="C160" s="4">
-        <v>1</v>
-      </c>
-      <c r="D160" s="4">
+      <c r="C160" s="2">
+        <v>1</v>
+      </c>
+      <c r="D160" s="2">
         <v>1</v>
       </c>
       <c r="E160" t="s">
@@ -17777,10 +17803,10 @@
       <c r="B161" t="s">
         <v>142</v>
       </c>
-      <c r="C161" s="4">
-        <v>1</v>
-      </c>
-      <c r="D161" s="4">
+      <c r="C161" s="2">
+        <v>1</v>
+      </c>
+      <c r="D161" s="2">
         <v>1</v>
       </c>
       <c r="E161" t="s">
@@ -17812,10 +17838,10 @@
       <c r="B162" t="s">
         <v>124</v>
       </c>
-      <c r="C162" s="4">
-        <v>1</v>
-      </c>
-      <c r="D162" s="4">
+      <c r="C162" s="2">
+        <v>1</v>
+      </c>
+      <c r="D162" s="2">
         <v>1</v>
       </c>
       <c r="E162" t="s">
@@ -17847,10 +17873,10 @@
       <c r="B163" t="s">
         <v>120</v>
       </c>
-      <c r="C163" s="4">
-        <v>1</v>
-      </c>
-      <c r="D163" s="4">
+      <c r="C163" s="2">
+        <v>1</v>
+      </c>
+      <c r="D163" s="2">
         <v>1</v>
       </c>
       <c r="E163" t="s">
@@ -17882,10 +17908,10 @@
       <c r="B164" t="s">
         <v>111</v>
       </c>
-      <c r="C164" s="4">
-        <v>1</v>
-      </c>
-      <c r="D164" s="4">
+      <c r="C164" s="2">
+        <v>1</v>
+      </c>
+      <c r="D164" s="2">
         <v>1</v>
       </c>
       <c r="E164" t="s">
@@ -17917,10 +17943,10 @@
       <c r="B165" t="s">
         <v>126</v>
       </c>
-      <c r="C165" s="4">
-        <v>1</v>
-      </c>
-      <c r="D165" s="4">
+      <c r="C165" s="2">
+        <v>1</v>
+      </c>
+      <c r="D165" s="2">
         <v>1</v>
       </c>
       <c r="E165" t="s">
@@ -17952,10 +17978,10 @@
       <c r="B166" t="s">
         <v>129</v>
       </c>
-      <c r="C166" s="4">
-        <v>1</v>
-      </c>
-      <c r="D166" s="4">
+      <c r="C166" s="2">
+        <v>1</v>
+      </c>
+      <c r="D166" s="2">
         <v>1</v>
       </c>
       <c r="E166" t="s">
@@ -17987,10 +18013,10 @@
       <c r="B167" t="s">
         <v>142</v>
       </c>
-      <c r="C167" s="4">
-        <v>1</v>
-      </c>
-      <c r="D167" s="4">
+      <c r="C167" s="2">
+        <v>1</v>
+      </c>
+      <c r="D167" s="2">
         <v>1</v>
       </c>
       <c r="E167" t="s">
@@ -18022,10 +18048,10 @@
       <c r="B168" t="s">
         <v>139</v>
       </c>
-      <c r="C168" s="4">
-        <v>1</v>
-      </c>
-      <c r="D168" s="4">
+      <c r="C168" s="2">
+        <v>1</v>
+      </c>
+      <c r="D168" s="2">
         <v>1</v>
       </c>
       <c r="E168" t="s">
@@ -18057,10 +18083,10 @@
       <c r="B169" t="s">
         <v>100</v>
       </c>
-      <c r="C169" s="4">
-        <v>1</v>
-      </c>
-      <c r="D169" s="4">
+      <c r="C169" s="2">
+        <v>1</v>
+      </c>
+      <c r="D169" s="2">
         <v>1</v>
       </c>
       <c r="E169" t="s">
@@ -18092,10 +18118,10 @@
       <c r="B170" t="s">
         <v>123</v>
       </c>
-      <c r="C170" s="4">
-        <v>1</v>
-      </c>
-      <c r="D170" s="4">
+      <c r="C170" s="2">
+        <v>1</v>
+      </c>
+      <c r="D170" s="2">
         <v>1</v>
       </c>
       <c r="E170" t="s">
@@ -18127,10 +18153,10 @@
       <c r="B171" t="s">
         <v>147</v>
       </c>
-      <c r="C171" s="4">
-        <v>1</v>
-      </c>
-      <c r="D171" s="4">
+      <c r="C171" s="2">
+        <v>1</v>
+      </c>
+      <c r="D171" s="2">
         <v>1</v>
       </c>
       <c r="E171" t="s">
@@ -18162,10 +18188,10 @@
       <c r="B172" t="s">
         <v>113</v>
       </c>
-      <c r="C172" s="4">
-        <v>1</v>
-      </c>
-      <c r="D172" s="4">
+      <c r="C172" s="2">
+        <v>1</v>
+      </c>
+      <c r="D172" s="2">
         <v>1</v>
       </c>
       <c r="E172" t="s">
@@ -18197,10 +18223,10 @@
       <c r="B173" t="s">
         <v>134</v>
       </c>
-      <c r="C173" s="4">
-        <v>1</v>
-      </c>
-      <c r="D173" s="4">
+      <c r="C173" s="2">
+        <v>1</v>
+      </c>
+      <c r="D173" s="2">
         <v>1</v>
       </c>
       <c r="E173" t="s">
@@ -18235,10 +18261,10 @@
       <c r="B174" t="s">
         <v>118</v>
       </c>
-      <c r="C174" s="4">
-        <v>1</v>
-      </c>
-      <c r="D174" s="4">
+      <c r="C174" s="2">
+        <v>1</v>
+      </c>
+      <c r="D174" s="2">
         <v>1</v>
       </c>
       <c r="E174" t="s">
@@ -18273,10 +18299,10 @@
       <c r="B175" t="s">
         <v>133</v>
       </c>
-      <c r="C175" s="4">
-        <v>1</v>
-      </c>
-      <c r="D175" s="4">
+      <c r="C175" s="2">
+        <v>1</v>
+      </c>
+      <c r="D175" s="2">
         <v>1</v>
       </c>
       <c r="E175" t="s">
@@ -18311,10 +18337,10 @@
       <c r="B176" t="s">
         <v>90</v>
       </c>
-      <c r="C176" s="4">
-        <v>1</v>
-      </c>
-      <c r="D176" s="4">
+      <c r="C176" s="2">
+        <v>1</v>
+      </c>
+      <c r="D176" s="2">
         <v>1</v>
       </c>
       <c r="E176" t="s">
@@ -18349,10 +18375,10 @@
       <c r="B177" t="s">
         <v>145</v>
       </c>
-      <c r="C177" s="4">
-        <v>1</v>
-      </c>
-      <c r="D177" s="4">
+      <c r="C177" s="2">
+        <v>1</v>
+      </c>
+      <c r="D177" s="2">
         <v>1</v>
       </c>
       <c r="E177" t="s">
@@ -18387,10 +18413,10 @@
       <c r="B178" t="s">
         <v>133</v>
       </c>
-      <c r="C178" s="4">
-        <v>1</v>
-      </c>
-      <c r="D178" s="4">
+      <c r="C178" s="2">
+        <v>1</v>
+      </c>
+      <c r="D178" s="2">
         <v>1</v>
       </c>
       <c r="E178" t="s">
@@ -18425,10 +18451,10 @@
       <c r="B179" t="s">
         <v>147</v>
       </c>
-      <c r="C179" s="4">
-        <v>1</v>
-      </c>
-      <c r="D179" s="4">
+      <c r="C179" s="2">
+        <v>1</v>
+      </c>
+      <c r="D179" s="2">
         <v>1</v>
       </c>
       <c r="E179" t="s">
@@ -18463,10 +18489,10 @@
       <c r="B180" t="s">
         <v>145</v>
       </c>
-      <c r="C180" s="4">
-        <v>1</v>
-      </c>
-      <c r="D180" s="4">
+      <c r="C180" s="2">
+        <v>1</v>
+      </c>
+      <c r="D180" s="2">
         <v>1</v>
       </c>
       <c r="E180" t="s">
@@ -18501,10 +18527,10 @@
       <c r="B181" t="s">
         <v>138</v>
       </c>
-      <c r="C181" s="4">
-        <v>1</v>
-      </c>
-      <c r="D181" s="4">
+      <c r="C181" s="2">
+        <v>1</v>
+      </c>
+      <c r="D181" s="2">
         <v>1</v>
       </c>
       <c r="E181" t="s">
@@ -18539,10 +18565,10 @@
       <c r="B182" t="s">
         <v>131</v>
       </c>
-      <c r="C182" s="4">
-        <v>1</v>
-      </c>
-      <c r="D182" s="4">
+      <c r="C182" s="2">
+        <v>1</v>
+      </c>
+      <c r="D182" s="2">
         <v>1</v>
       </c>
       <c r="Q182" t="s">
@@ -18565,10 +18591,10 @@
       <c r="B183" t="s">
         <v>134</v>
       </c>
-      <c r="C183" s="4">
-        <v>1</v>
-      </c>
-      <c r="D183" s="4">
+      <c r="C183" s="2">
+        <v>1</v>
+      </c>
+      <c r="D183" s="2">
         <v>1</v>
       </c>
       <c r="Q183" t="s">
@@ -18591,10 +18617,10 @@
       <c r="B184" t="s">
         <v>139</v>
       </c>
-      <c r="C184" s="4">
-        <v>1</v>
-      </c>
-      <c r="D184" s="4">
+      <c r="C184" s="2">
+        <v>1</v>
+      </c>
+      <c r="D184" s="2">
         <v>1</v>
       </c>
       <c r="Q184" t="s">
@@ -18617,10 +18643,10 @@
       <c r="B185" t="s">
         <v>132</v>
       </c>
-      <c r="C185" s="4">
-        <v>1</v>
-      </c>
-      <c r="D185" s="4">
+      <c r="C185" s="2">
+        <v>1</v>
+      </c>
+      <c r="D185" s="2">
         <v>1</v>
       </c>
       <c r="Q185" t="s">
@@ -18643,10 +18669,10 @@
       <c r="B186" t="s">
         <v>148</v>
       </c>
-      <c r="C186" s="4">
-        <v>1</v>
-      </c>
-      <c r="D186" s="4">
+      <c r="C186" s="2">
+        <v>1</v>
+      </c>
+      <c r="D186" s="2">
         <v>1</v>
       </c>
       <c r="Q186" t="s">
@@ -18669,10 +18695,10 @@
       <c r="B187" t="s">
         <v>131</v>
       </c>
-      <c r="C187" s="4">
-        <v>1</v>
-      </c>
-      <c r="D187" s="4">
+      <c r="C187" s="2">
+        <v>1</v>
+      </c>
+      <c r="D187" s="2">
         <v>1</v>
       </c>
       <c r="Q187" t="s">
@@ -18695,10 +18721,10 @@
       <c r="B188" t="s">
         <v>121</v>
       </c>
-      <c r="C188" s="4">
-        <v>1</v>
-      </c>
-      <c r="D188" s="4">
+      <c r="C188" s="2">
+        <v>1</v>
+      </c>
+      <c r="D188" s="2">
         <v>1</v>
       </c>
       <c r="Q188" t="s">
@@ -18721,10 +18747,10 @@
       <c r="B189" t="s">
         <v>146</v>
       </c>
-      <c r="C189" s="4">
-        <v>1</v>
-      </c>
-      <c r="D189" s="4">
+      <c r="C189" s="2">
+        <v>1</v>
+      </c>
+      <c r="D189" s="2">
         <v>1</v>
       </c>
       <c r="Q189" t="s">
@@ -18741,10 +18767,10 @@
       <c r="B190" t="s">
         <v>121</v>
       </c>
-      <c r="C190" s="4">
-        <v>1</v>
-      </c>
-      <c r="D190" s="4">
+      <c r="C190" s="2">
+        <v>1</v>
+      </c>
+      <c r="D190" s="2">
         <v>1</v>
       </c>
       <c r="Q190" t="s">
@@ -18761,10 +18787,10 @@
       <c r="B191" t="s">
         <v>96</v>
       </c>
-      <c r="C191" s="4">
-        <v>1</v>
-      </c>
-      <c r="D191" s="4">
+      <c r="C191" s="2">
+        <v>1</v>
+      </c>
+      <c r="D191" s="2">
         <v>1</v>
       </c>
       <c r="Q191" t="s">
@@ -18781,10 +18807,10 @@
       <c r="B192" t="s">
         <v>134</v>
       </c>
-      <c r="C192" s="4">
-        <v>1</v>
-      </c>
-      <c r="D192" s="4">
+      <c r="C192" s="2">
+        <v>1</v>
+      </c>
+      <c r="D192" s="2">
         <v>1</v>
       </c>
       <c r="Q192" t="s">
@@ -18801,10 +18827,10 @@
       <c r="B193" t="s">
         <v>105</v>
       </c>
-      <c r="C193" s="4">
-        <v>1</v>
-      </c>
-      <c r="D193" s="4">
+      <c r="C193" s="2">
+        <v>1</v>
+      </c>
+      <c r="D193" s="2">
         <v>1</v>
       </c>
       <c r="Q193" t="s">
@@ -18821,10 +18847,10 @@
       <c r="B194" t="s">
         <v>148</v>
       </c>
-      <c r="C194" s="4">
-        <v>1</v>
-      </c>
-      <c r="D194" s="4">
+      <c r="C194" s="2">
+        <v>1</v>
+      </c>
+      <c r="D194" s="2">
         <v>1</v>
       </c>
       <c r="Q194" t="s">
